--- a/docs/Anvil/pythonfiles/compliment_kit.xlsx
+++ b/docs/Anvil/pythonfiles/compliment_kit.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://paradevic-my.sharepoint.com/personal/gmccarthy_parade_vic_edu_au/Documents/All DT/microbit for online/PC-app-development/docs/Anvil/pythonfiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{70589EC8-7625-4359-B542-A6E55D2C5F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4254AD52-C8A7-457B-BB86-2303712F1E27}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{70589EC8-7625-4359-B542-A6E55D2C5F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FEA98D4-F5AD-45AE-B587-DDEFBF8C65B4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10170" yWindow="840" windowWidth="10815" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet5" sheetId="7" r:id="rId1"/>
+    <sheet name="sheet1" sheetId="7" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
